--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121276046</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,6 +788,131 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121407739</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57367</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vitterberg, Töftedal, Dals Ed, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>314896</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6523159</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack i en död tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog i i kanten av våtmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121276046</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121407739</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121276046</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121407739</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121276046</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121407739</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121276046</v>
+        <v>121407739</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vitteberg, Dls</t>
+          <t>Vitterberg, Töftedal, Dals Ed, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>314884</v>
+        <v>314896</v>
       </c>
       <c r="R2" t="n">
-        <v>6523094</v>
+        <v>6523159</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack i en död tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,30 +770,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Blandskog i i kanten av våtmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Pixel Petersson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Pixel Petersson</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121407739</v>
+        <v>121276046</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,17 +834,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vitterberg, Töftedal, Dals Ed, Dls</t>
+          <t>Vitteberg, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>314896</v>
+        <v>314884</v>
       </c>
       <c r="R3" t="n">
-        <v>6523159</v>
+        <v>6523094</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +868,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack i en död tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,25 +890,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog i i kanten av våtmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Per Pixel Petersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Per Pixel Petersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 47665-2024 artfynd.xlsx
+++ b/artfynd/A 47665-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121407739</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,8 +912,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121276046</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>